--- a/Calculations/Timeout_calculation.xlsx
+++ b/Calculations/Timeout_calculation.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="21120" windowHeight="12600"/>
@@ -11,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
   <si>
     <t>Miliseconds</t>
   </si>
@@ -97,13 +97,43 @@
   </si>
   <si>
     <t>hi</t>
+  </si>
+  <si>
+    <t>Cr speed</t>
+  </si>
+  <si>
+    <t>machine period</t>
+  </si>
+  <si>
+    <t>sec</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>Target freq</t>
+  </si>
+  <si>
+    <t>kHz</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>Target period</t>
+  </si>
+  <si>
+    <t>Target clock ticks sleep for freq</t>
+  </si>
+  <si>
+    <t>Target basic instructions for sleep</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +186,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -234,6 +269,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -268,6 +304,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -443,17 +480,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.375" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="8" width="12" hidden="1" customWidth="1"/>
     <col min="9" max="11" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -474,7 +512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -533,7 +571,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -592,7 +630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>300</v>
       </c>
@@ -663,60 +701,60 @@
         <v>40</v>
       </c>
       <c r="U4" s="4">
-        <f>A$12/A4*U$12</f>
+        <f t="shared" ref="U4:U11" si="5">A$12/A4*U$12</f>
         <v>192</v>
       </c>
       <c r="V4" s="4">
         <v>0</v>
       </c>
       <c r="X4" s="4" t="str">
-        <f t="shared" ref="X4:X12" si="5">DEC2HEX(255-U4+1)</f>
+        <f t="shared" ref="X4:X12" si="6">DEC2HEX(255-U4+1)</f>
         <v>40</v>
       </c>
       <c r="Y4" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1200</v>
       </c>
       <c r="B5">
-        <f t="shared" ref="B5:B12" si="6">1000/A5</f>
+        <f t="shared" ref="B5:B12" si="7">1000/A5</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:C12" si="7">B5*10</f>
+        <f t="shared" ref="C5:C12" si="8">B5*10</f>
         <v>8.3333333333333339</v>
       </c>
       <c r="D5" s="1">
-        <f t="shared" ref="D5:D12" si="8">C5*15</f>
+        <f t="shared" ref="D5:D12" si="9">C5*15</f>
         <v>125.00000000000001</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E12" si="9">D5*4</f>
+        <f t="shared" ref="E5:E12" si="10">D5*4</f>
         <v>500.00000000000006</v>
       </c>
       <c r="F5">
         <v>24</v>
       </c>
       <c r="G5">
-        <f t="shared" ref="G5:G9" si="10">F5*F$1</f>
+        <f t="shared" ref="G5:G9" si="11">F5*F$1</f>
         <v>2.6041666666666668E-2</v>
       </c>
       <c r="H5">
-        <f t="shared" ref="H5:H9" si="11">D5/G5</f>
+        <f t="shared" ref="H5:H9" si="12">D5/G5</f>
         <v>4800</v>
       </c>
       <c r="I5">
         <v>48</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5:J12" si="12">F$1*I5</f>
+        <f t="shared" ref="J5:J12" si="13">F$1*I5</f>
         <v>5.2083333333333336E-2</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K12" si="13">D5/J5</f>
+        <f t="shared" ref="K5:K12" si="14">D5/J5</f>
         <v>2400</v>
       </c>
       <c r="L5">
@@ -736,7 +774,7 @@
         <v>580</v>
       </c>
       <c r="P5">
-        <f t="shared" ref="P5:P10" si="14">A$12/A5</f>
+        <f t="shared" ref="P5:P10" si="15">A$12/A5</f>
         <v>48</v>
       </c>
       <c r="Q5" s="3">
@@ -744,70 +782,70 @@
         <v>48</v>
       </c>
       <c r="R5" s="3" t="str">
-        <f t="shared" ref="R5:R12" si="15">DEC2HEX(255-M5+1)</f>
+        <f t="shared" ref="R5:R11" si="16">DEC2HEX(255-M5+1)</f>
         <v>E8</v>
       </c>
       <c r="S5" s="3" t="str">
-        <f t="shared" ref="S5:S12" si="16">DEC2HEX(255-Q5+1)</f>
+        <f t="shared" ref="S5:S12" si="17">DEC2HEX(255-Q5+1)</f>
         <v>D0</v>
       </c>
       <c r="U5" s="4">
-        <f>A$12/A5*U$12</f>
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="V5" s="4">
-        <f>A$13/A5*V$13</f>
+        <f t="shared" ref="V5:V12" si="18">A$13/A5*V$13</f>
         <v>96</v>
       </c>
       <c r="X5" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>D0</v>
       </c>
       <c r="Y5" s="4" t="str">
-        <f>DEC2HEX(255-V5+1)</f>
+        <f t="shared" ref="Y5:Y13" si="19">DEC2HEX(255-V5+1)</f>
         <v>A0</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2400</v>
       </c>
       <c r="B6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.41666666666666669</v>
       </c>
       <c r="C6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.166666666666667</v>
       </c>
       <c r="D6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>62.500000000000007</v>
       </c>
       <c r="E6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>250.00000000000003</v>
       </c>
       <c r="F6">
         <v>12</v>
       </c>
       <c r="G6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3020833333333334E-2</v>
       </c>
       <c r="H6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4800</v>
       </c>
       <c r="I6">
         <v>24</v>
       </c>
       <c r="J6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.6041666666666668E-2</v>
       </c>
       <c r="K6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2400</v>
       </c>
       <c r="L6">
@@ -827,7 +865,7 @@
         <v>340</v>
       </c>
       <c r="P6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="Q6" s="3">
@@ -835,70 +873,70 @@
         <v>24</v>
       </c>
       <c r="R6" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>F4</v>
       </c>
       <c r="S6" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>E8</v>
       </c>
       <c r="U6" s="4">
-        <f>A$12/A6*U$12</f>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="V6" s="4">
-        <f>A$13/A6*V$13</f>
+        <f t="shared" si="18"/>
         <v>48</v>
       </c>
       <c r="X6" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>E8</v>
       </c>
       <c r="Y6" s="4" t="str">
-        <f>DEC2HEX(255-V6+1)</f>
+        <f t="shared" si="19"/>
         <v>D0</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4800</v>
       </c>
       <c r="B7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.20833333333333334</v>
       </c>
       <c r="C7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.0833333333333335</v>
       </c>
       <c r="D7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>31.250000000000004</v>
       </c>
       <c r="E7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>125.00000000000001</v>
       </c>
       <c r="F7">
         <v>6</v>
       </c>
       <c r="G7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.510416666666667E-3</v>
       </c>
       <c r="H7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4800</v>
       </c>
       <c r="I7">
         <v>12</v>
       </c>
       <c r="J7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.3020833333333334E-2</v>
       </c>
       <c r="K7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2400</v>
       </c>
       <c r="L7">
@@ -918,7 +956,7 @@
         <v>220</v>
       </c>
       <c r="P7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="Q7" s="3">
@@ -926,70 +964,70 @@
         <v>12</v>
       </c>
       <c r="R7" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>FA</v>
       </c>
       <c r="S7" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>F4</v>
       </c>
       <c r="U7" s="4">
-        <f>A$12/A7*U$12</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="V7" s="4">
-        <f>A$13/A7*V$13</f>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="X7" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>F4</v>
       </c>
       <c r="Y7" s="4" t="str">
-        <f>DEC2HEX(255-V7+1)</f>
+        <f t="shared" si="19"/>
         <v>E8</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9600</v>
       </c>
       <c r="B8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10416666666666667</v>
       </c>
       <c r="C8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.0416666666666667</v>
       </c>
       <c r="D8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>15.625000000000002</v>
       </c>
       <c r="E8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>62.500000000000007</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.2552083333333335E-3</v>
       </c>
       <c r="H8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4800</v>
       </c>
       <c r="I8">
         <v>6</v>
       </c>
       <c r="J8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.510416666666667E-3</v>
       </c>
       <c r="K8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2400</v>
       </c>
       <c r="L8">
@@ -1009,7 +1047,7 @@
         <v>160</v>
       </c>
       <c r="P8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
       <c r="Q8" s="3">
@@ -1017,70 +1055,70 @@
         <v>6</v>
       </c>
       <c r="R8" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>FD</v>
       </c>
       <c r="S8" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>FA</v>
       </c>
       <c r="U8" s="4">
-        <f>A$12/A8*U$12</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="V8" s="4">
-        <f>A$13/A8*V$13</f>
+        <f t="shared" si="18"/>
         <v>12</v>
       </c>
       <c r="X8" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>FA</v>
       </c>
       <c r="Y8" s="4" t="str">
-        <f>DEC2HEX(255-V8+1)</f>
+        <f t="shared" si="19"/>
         <v>F4</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>14400</v>
       </c>
       <c r="B9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.9444444444444448E-2</v>
       </c>
       <c r="C9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.69444444444444442</v>
       </c>
       <c r="D9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.416666666666666</v>
       </c>
       <c r="E9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>41.666666666666664</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.170138888888889E-3</v>
       </c>
       <c r="H9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4799.9999999999991</v>
       </c>
       <c r="I9">
         <v>4</v>
       </c>
       <c r="J9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.340277777777778E-3</v>
       </c>
       <c r="K9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2399.9999999999995</v>
       </c>
       <c r="L9">
@@ -1100,7 +1138,7 @@
         <v>140</v>
       </c>
       <c r="P9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="Q9" s="3">
@@ -1108,59 +1146,59 @@
         <v>4</v>
       </c>
       <c r="R9" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>FE</v>
       </c>
       <c r="S9" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>FC</v>
       </c>
       <c r="U9" s="4">
-        <f>A$12/A9*U$12</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="V9" s="4">
-        <f>A$13/A9*V$13</f>
+        <f t="shared" si="18"/>
         <v>8</v>
       </c>
       <c r="X9" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>FC</v>
       </c>
       <c r="Y9" s="4" t="str">
-        <f>DEC2HEX(255-V9+1)</f>
+        <f t="shared" si="19"/>
         <v>F8</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>19200</v>
       </c>
       <c r="B10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.2083333333333336E-2</v>
       </c>
       <c r="C10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.52083333333333337</v>
       </c>
       <c r="D10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7.8125000000000009</v>
       </c>
       <c r="E10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31.250000000000004</v>
       </c>
       <c r="I10">
         <v>3</v>
       </c>
       <c r="J10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.2552083333333335E-3</v>
       </c>
       <c r="K10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2400</v>
       </c>
       <c r="M10" s="2"/>
@@ -1173,7 +1211,7 @@
         <v>130</v>
       </c>
       <c r="P10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="Q10" s="3">
@@ -1182,44 +1220,44 @@
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>FD</v>
       </c>
       <c r="U10" s="4">
-        <f>A$12/A10*U$12</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="V10" s="4">
-        <f>A$13/A10*V$13</f>
+        <f t="shared" si="18"/>
         <v>6</v>
       </c>
       <c r="X10" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>FD</v>
       </c>
       <c r="Y10" s="4" t="str">
-        <f>DEC2HEX(255-V10+1)</f>
+        <f t="shared" si="19"/>
         <v>FA</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>28800</v>
       </c>
       <c r="B11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.4722222222222224E-2</v>
       </c>
       <c r="C11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.34722222222222221</v>
       </c>
       <c r="D11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.208333333333333</v>
       </c>
       <c r="E11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20.833333333333332</v>
       </c>
       <c r="F11">
@@ -1237,11 +1275,11 @@
         <v>2</v>
       </c>
       <c r="J11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.170138888888889E-3</v>
       </c>
       <c r="K11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2399.9999999999995</v>
       </c>
       <c r="L11">
@@ -1266,59 +1304,59 @@
         <v>2</v>
       </c>
       <c r="R11" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>FF</v>
       </c>
       <c r="S11" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>FE</v>
       </c>
       <c r="U11" s="4">
-        <f>A$12/A11*U$12</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V11" s="4">
-        <f>A$13/A11*V$13</f>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="X11" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>FE</v>
       </c>
       <c r="Y11" s="4" t="str">
-        <f>DEC2HEX(255-V11+1)</f>
+        <f t="shared" si="19"/>
         <v>FC</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>57600</v>
       </c>
       <c r="B12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.7361111111111112E-2</v>
       </c>
       <c r="C12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.1736111111111111</v>
       </c>
       <c r="D12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.6041666666666665</v>
       </c>
       <c r="E12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10.416666666666666</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="J12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.0850694444444445E-3</v>
       </c>
       <c r="K12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2399.9999999999995</v>
       </c>
       <c r="M12" s="2"/>
@@ -1338,26 +1376,26 @@
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>FF</v>
       </c>
       <c r="U12" s="4">
         <v>1</v>
       </c>
       <c r="V12" s="4">
-        <f>A$13/A12*V$13</f>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="X12" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>FF</v>
       </c>
       <c r="Y12" s="4" t="str">
-        <f>DEC2HEX(255-V12+1)</f>
+        <f t="shared" si="19"/>
         <v>FE</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>115200</v>
       </c>
@@ -1379,8 +1417,99 @@
       </c>
       <c r="X13" s="4"/>
       <c r="Y13" s="4" t="str">
-        <f>DEC2HEX(255-V13+1)</f>
+        <f t="shared" si="19"/>
         <v>FF</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18">
+        <f>1/(22.184*1000000)</f>
+        <v>4.5077533357374683E-8</v>
+      </c>
+      <c r="M18">
+        <f>L18*1000</f>
+        <v>4.5077533357374686E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19">
+        <f>L18*12</f>
+        <v>5.4093040028849617E-7</v>
+      </c>
+      <c r="M19">
+        <f>L19*1000</f>
+        <v>5.4093040028849616E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="L22">
+        <v>10</v>
+      </c>
+      <c r="M22">
+        <f>L22*1000</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N23">
+        <f>1/M22</f>
+        <v>1E-4</v>
+      </c>
+      <c r="O23">
+        <f>N23*1000</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="L25">
+        <f>O23/M19</f>
+        <v>184.8666666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26">
+        <f>L25/12</f>
+        <v>15.405555555555559</v>
       </c>
     </row>
   </sheetData>
@@ -1389,18 +1518,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
